--- a/workbooks/csc_program_collection_queue.xlsx
+++ b/workbooks/csc_program_collection_queue.xlsx
@@ -27,8 +27,8 @@
   <dc:title>Collection Queue</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T04:36:57Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T04:36:57Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T04:46:20Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T04:46:20Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 

--- a/workbooks/csc_program_collection_queue.xlsx
+++ b/workbooks/csc_program_collection_queue.xlsx
@@ -27,8 +27,8 @@
   <dc:title>Collection Queue</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T04:46:20Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T04:46:20Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T04:53:14Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T04:53:14Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 

--- a/workbooks/csc_program_collection_queue.xlsx
+++ b/workbooks/csc_program_collection_queue.xlsx
@@ -27,8 +27,8 @@
   <dc:title>Collection Queue</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T04:53:14Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T04:53:14Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:02:34Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:02:34Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 

--- a/workbooks/csc_program_collection_queue.xlsx
+++ b/workbooks/csc_program_collection_queue.xlsx
@@ -27,8 +27,8 @@
   <dc:title>Collection Queue</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:02:34Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:02:34Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:08:21Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:08:21Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 

--- a/workbooks/csc_program_collection_queue.xlsx
+++ b/workbooks/csc_program_collection_queue.xlsx
@@ -27,8 +27,8 @@
   <dc:title>Collection Queue</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:08:21Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:08:21Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:17:49Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:17:49Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 

--- a/workbooks/csc_program_collection_queue.xlsx
+++ b/workbooks/csc_program_collection_queue.xlsx
@@ -27,8 +27,8 @@
   <dc:title>Collection Queue</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:17:49Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:17:49Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:30:43Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:30:43Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 

--- a/workbooks/csc_program_collection_queue.xlsx
+++ b/workbooks/csc_program_collection_queue.xlsx
@@ -27,8 +27,8 @@
   <dc:title>Collection Queue</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:30:43Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:30:43Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:41:36Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:41:36Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 

--- a/workbooks/csc_program_collection_queue.xlsx
+++ b/workbooks/csc_program_collection_queue.xlsx
@@ -27,8 +27,8 @@
   <dc:title>Collection Queue</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:41:36Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:41:36Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:57:18Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:57:18Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 
